--- a/R-cds2db/cds2db/inst/extdata/Table_Description_Definition.xlsx
+++ b/R-cds2db/cds2db/inst/extdata/Table_Description_Definition.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="263">
   <si>
     <t xml:space="preserve">RESOURCE</t>
   </si>
@@ -474,6 +474,12 @@
   </si>
   <si>
     <t xml:space="preserve">dateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">policy/authority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">policy/uri</t>
   </si>
   <si>
     <t xml:space="preserve">provision/Provision</t>
@@ -1217,8 +1223,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G234"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G237"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27.86"/>
@@ -1430,7 +1436,7 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="4" t="s">
         <v>36</v>
       </c>
@@ -1945,7 +1951,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
         <v>104</v>
       </c>
@@ -2031,7 +2037,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C127" s="4" t="s">
         <v>106</v>
       </c>
@@ -2042,13 +2048,13 @@
       <c r="F127" s="3"/>
       <c r="G127" s="3"/>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C128" s="4" t="s">
         <v>107</v>
       </c>
       <c r="D128" s="4"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C129" s="4" t="s">
         <v>108</v>
       </c>
@@ -2074,7 +2080,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="s">
         <v>110</v>
       </c>
@@ -2185,7 +2191,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C152" s="4" t="s">
         <v>119</v>
       </c>
@@ -2228,7 +2234,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="s">
         <v>127</v>
       </c>
@@ -2314,7 +2320,7 @@
       <c r="F171" s="3"/>
       <c r="G171" s="3"/>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C172" s="4" t="s">
         <v>119</v>
       </c>
@@ -2332,7 +2338,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="s">
         <v>133</v>
       </c>
@@ -2398,13 +2404,13 @@
       <c r="F184" s="3"/>
       <c r="G184" s="3"/>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C185" s="4" t="s">
         <v>83</v>
       </c>
       <c r="D185" s="4"/>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C186" s="4" t="s">
         <v>119</v>
       </c>
@@ -2415,7 +2421,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="s">
         <v>136</v>
       </c>
@@ -2506,7 +2512,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="s">
         <v>140</v>
       </c>
@@ -2539,129 +2545,115 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C208" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F208" s="3"/>
-      <c r="G208" s="3"/>
+        <v>44</v>
+      </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C209" s="1" t="s">
-        <v>145</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F209" s="3"/>
+      <c r="G209" s="3"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C210" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F210" s="3"/>
+      <c r="G210" s="3"/>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C211" s="1" t="s">
         <v>146</v>
       </c>
+      <c r="F211" s="3"/>
+      <c r="G211" s="3"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B212" s="3" t="s">
+      <c r="C212" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C212" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D212" s="3"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C213" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F213" s="3"/>
-      <c r="G213" s="3"/>
-    </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C214" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F214" s="3"/>
-      <c r="G214" s="3"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C215" s="1" t="s">
+      <c r="A215" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B215" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F215" s="3"/>
-      <c r="G215" s="3"/>
+      <c r="C215" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D215" s="3"/>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C216" s="1" t="s">
-        <v>150</v>
+        <v>14</v>
       </c>
       <c r="F216" s="3"/>
       <c r="G216" s="3"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C217" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F217" s="3"/>
+      <c r="G217" s="3"/>
+    </row>
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C218" s="1" t="s">
         <v>151</v>
       </c>
+      <c r="F218" s="3"/>
+      <c r="G218" s="3"/>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="3" t="s">
+      <c r="C219" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B219" s="3"/>
-      <c r="C219" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D219" s="3"/>
       <c r="F219" s="3"/>
       <c r="G219" s="3"/>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C220" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="F220" s="3"/>
-      <c r="G220" s="3"/>
-    </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C221" s="1" t="s">
+      <c r="B222" s="3"/>
+      <c r="C222" s="3" t="s">
         <v>155</v>
       </c>
+      <c r="D222" s="3"/>
+      <c r="F222" s="3"/>
+      <c r="G222" s="3"/>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="3" t="s">
+      <c r="C223" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B223" s="3"/>
-      <c r="C223" s="3"/>
-      <c r="D223" s="3"/>
-      <c r="E223" s="3"/>
       <c r="F223" s="3"/>
       <c r="G223" s="3"/>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="3" t="s">
+      <c r="C224" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B224" s="3"/>
-      <c r="C224" s="3"/>
-      <c r="D224" s="3"/>
-      <c r="E224" s="3"/>
-      <c r="F224" s="3"/>
-      <c r="G224" s="3"/>
-    </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B225" s="3"/>
-      <c r="C225" s="3"/>
-      <c r="D225" s="3"/>
-      <c r="E225" s="3"/>
-      <c r="F225" s="3"/>
-      <c r="G225" s="3"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
@@ -2671,93 +2663,126 @@
       <c r="G226" s="3"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="2" t="s">
+      <c r="A227" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B227" s="3"/>
+      <c r="C227" s="3"/>
+      <c r="D227" s="3"/>
+      <c r="E227" s="3"/>
+      <c r="F227" s="3"/>
+      <c r="G227" s="3"/>
+    </row>
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B227" s="2" t="s">
+      <c r="B228" s="3"/>
+      <c r="C228" s="3"/>
+      <c r="D228" s="3"/>
+      <c r="E228" s="3"/>
+      <c r="F228" s="3"/>
+      <c r="G228" s="3"/>
+    </row>
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="3" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="6" t="s">
+      <c r="B229" s="3"/>
+      <c r="C229" s="3"/>
+      <c r="D229" s="3"/>
+      <c r="E229" s="3"/>
+      <c r="F229" s="3"/>
+      <c r="G229" s="3"/>
+    </row>
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B228" s="6" t="s">
+      <c r="B230" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="B229" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="E229" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="B230" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E230" s="3" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="6" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="6" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="6" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B236" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B234" s="6" t="s">
+      <c r="E236" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E234" s="3" t="s">
+    </row>
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="6" t="s">
         <v>182</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="E7:E220" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="E7:E223" type="list">
       <formula1>Datatypes!$A$2:$A$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2778,7 +2803,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.14"/>
@@ -2795,33 +2820,33 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B6" s="3"/>
     </row>
@@ -2842,7 +2867,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.14"/>
@@ -2859,13 +2884,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B3" s="3"/>
     </row>
@@ -2886,7 +2911,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.14"/>
@@ -2903,27 +2928,27 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B5" s="3"/>
     </row>
@@ -2944,7 +2969,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.14"/>
@@ -2961,33 +2986,33 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B6" s="3"/>
     </row>
@@ -3008,7 +3033,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.14"/>
@@ -3025,19 +3050,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>37</v>
@@ -3045,7 +3070,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B5" s="3"/>
     </row>
@@ -3066,7 +3091,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.14"/>
@@ -3083,13 +3108,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B3" s="3"/>
     </row>
@@ -3110,7 +3135,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="10.14"/>
@@ -3127,30 +3152,30 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -3170,7 +3195,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="43.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="10.14"/>
@@ -3187,7 +3212,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
@@ -3195,27 +3220,27 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>70</v>
@@ -3223,17 +3248,17 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3243,47 +3268,47 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3303,7 +3328,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="10.14"/>
@@ -3320,7 +3345,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>37</v>
@@ -3328,22 +3353,22 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>22</v>
@@ -3351,7 +3376,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>22</v>
@@ -3359,28 +3384,28 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>22</v>
@@ -3388,7 +3413,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>22</v>
@@ -3396,46 +3421,46 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>22</v>
@@ -3463,7 +3488,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="10.14"/>
@@ -3480,7 +3505,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3490,12 +3515,12 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3505,7 +3530,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -3525,7 +3550,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.14"/>
@@ -3542,19 +3567,19 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>37</v>
@@ -3562,13 +3587,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B6" s="3"/>
     </row>
@@ -3583,8 +3608,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffSeite &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;KffffffSeite &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3595,25 +3620,25 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3628,7 +3653,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3643,7 +3668,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -3663,7 +3688,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.14"/>
@@ -3680,31 +3705,31 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B6" s="3"/>
     </row>
@@ -3725,7 +3750,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.14"/>
@@ -3742,43 +3767,43 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B8" s="3"/>
     </row>
@@ -3799,7 +3824,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="10.16"/>
@@ -3815,17 +3840,17 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3853,8 +3878,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3865,7 +3890,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.14"/>
@@ -3882,13 +3907,13 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B3" s="3"/>
     </row>
@@ -3909,7 +3934,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.14"/>
@@ -3926,25 +3951,25 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B5" s="3"/>
     </row>
@@ -3965,7 +3990,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.14"/>
@@ -3982,7 +4007,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>37</v>
@@ -3990,7 +4015,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>37</v>
@@ -4013,7 +4038,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58984375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.14"/>
@@ -4030,25 +4055,25 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B5" s="3"/>
     </row>

--- a/R-cds2db/cds2db/inst/extdata/Table_Description_Definition.xlsx
+++ b/R-cds2db/cds2db/inst/extdata/Table_Description_Definition.xlsx
@@ -37,7 +37,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -85,6 +85,9 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -119,7 +122,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -173,6 +176,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -3457,7 +3463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="12" min="1" max="1"/>
@@ -3467,149 +3473,171 @@
     <col width="26" customWidth="1" style="12" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+    <row r="1" s="12">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Hint</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr"/>
-      <c r="C1" s="16" t="inlineStr"/>
-      <c r="D1" s="16" t="inlineStr"/>
-      <c r="E1" s="16" t="inlineStr"/>
-    </row>
-    <row r="2" ht="45" customHeight="1" s="12">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Dieses Blatt beschreibt Snapshot-spezifische Anreicherungsspalten. Diese Spalten werden nicht beim normalen Toolchain-DB-Init erzeugt, sondern nur beim Aufbau pseudonymisierter Snapshot-DBs ergänzt.</t>
-        </is>
-      </c>
-      <c r="B2" s="18" t="inlineStr"/>
-      <c r="C2" s="18" t="inlineStr"/>
-      <c r="D2" s="18" t="inlineStr"/>
-      <c r="E2" s="18" t="inlineStr"/>
-    </row>
-    <row r="3" ht="30" customHeight="1" s="12">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>Der Snapshot-Prozess liest dieses Blatt zusätzlich zur normalen Table Description; operative Generatoren sollen es ignorieren.</t>
-        </is>
-      </c>
-      <c r="B3" s="18" t="inlineStr"/>
-      <c r="C3" s="18" t="inlineStr"/>
-      <c r="D3" s="18" t="inlineStr"/>
-      <c r="E3" s="18" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="18" t="inlineStr"/>
-      <c r="B4" s="18" t="inlineStr"/>
-      <c r="C4" s="18" t="inlineStr"/>
-      <c r="D4" s="18" t="inlineStr"/>
-      <c r="E4" s="18" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="19" t="n"/>
+      <c r="D1" s="19" t="n"/>
+      <c r="E1" s="19" t="n"/>
+    </row>
+    <row r="2" s="12">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Dieses Blatt beschreibt Snapshot-spezifische Anreicherungsspalten.</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+    </row>
+    <row r="3" s="12">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>Diese Spalten werden nicht beim normalen Toolchain-DB-Init erzeugt.</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="n"/>
+      <c r="C3" s="19" t="n"/>
+      <c r="D3" s="19" t="n"/>
+      <c r="E3" s="19" t="n"/>
+    </row>
+    <row r="4" s="12">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>Der Snapshot-Prozess liest dieses Blatt zusätzlich zur normalen Table Description.</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="n"/>
+    </row>
+    <row r="5" s="12">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>Operative Generatoren sollen dieses Blatt ignorieren.</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+    </row>
+    <row r="6" s="12">
+      <c r="A6" s="19" t="n"/>
+      <c r="B6" s="19" t="n"/>
+      <c r="C6" s="19" t="n"/>
+      <c r="D6" s="19" t="n"/>
+      <c r="E6" s="19" t="n"/>
+    </row>
+    <row r="7" s="12">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>TABLE_NAME</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>COLUMN_NAME</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>COLUMN_DESCRIPTION</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>COLUMN_TYPE</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>PSEUDONYMIZATION_RULE</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="8" s="12">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>observation</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>value_in_reference_unit</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Wert in Referenzeinheit</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>double precision</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>keep</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>observation</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>reference_unit</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Referenzeinheit</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>varchar</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>keep</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>observation</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>primary_loinc_code</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>Primary LOINC Code</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>varchar</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>keep</t>
         </is>

--- a/R-cds2db/cds2db/inst/extdata/Table_Description_Definition.xlsx
+++ b/R-cds2db/cds2db/inst/extdata/Table_Description_Definition.xlsx
@@ -3463,7 +3463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="12" min="1" max="1"/>
@@ -3638,6 +3638,168 @@
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>medicationrequest</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>medreq_medication_system</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>Codesystem der referenzierten Medication</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>medicationrequest</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>medreq_medication_code</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>Code der referenzierten Medication</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>medicationadministration</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>medadm_medication_system</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>Codesystem der referenzierten Medication</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>medicationadministration</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>medadm_medication_code</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>Code der referenzierten Medication</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>medicationstatement</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>medstat_medication_system</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Codesystem der referenzierten Medication</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>medicationstatement</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>medstat_medication_code</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Code der referenzierten Medication</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>keep</t>
         </is>

--- a/R-cds2db/cds2db/inst/extdata/Table_Description_Definition.xlsx
+++ b/R-cds2db/cds2db/inst/extdata/Table_Description_Definition.xlsx
@@ -3463,7 +3463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="12" min="1" max="1"/>
@@ -3565,22 +3565,22 @@
     <row r="8" s="12">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>observation</t>
+          <t>medicationrequest</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>value_in_reference_unit</t>
+          <t>medreq_medication_system</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>Wert in Referenzeinheit</t>
+          <t>Codesystem der referenzierten Medication</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>double precision</t>
+          <t>varchar</t>
         </is>
       </c>
       <c r="E8" s="19" t="inlineStr">
@@ -3592,17 +3592,17 @@
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>observation</t>
+          <t>medicationrequest</t>
         </is>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>reference_unit</t>
+          <t>medreq_medication_code</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>Referenzeinheit</t>
+          <t>Code der referenzierten Medication</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -3619,17 +3619,17 @@
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>observation</t>
+          <t>medicationadministration</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>primary_loinc_code</t>
+          <t>medadm_medication_system</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>Primary LOINC Code</t>
+          <t>Codesystem der referenzierten Medication</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
@@ -3646,17 +3646,17 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>medicationrequest</t>
+          <t>medicationadministration</t>
         </is>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>medreq_medication_system</t>
+          <t>medadm_medication_code</t>
         </is>
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>Codesystem der referenzierten Medication</t>
+          <t>Code der referenzierten Medication</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -3673,17 +3673,17 @@
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>medicationrequest</t>
+          <t>medicationstatement</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>medreq_medication_code</t>
+          <t>medstat_medication_system</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>Code der referenzierten Medication</t>
+          <t>Codesystem der referenzierten Medication</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
@@ -3700,17 +3700,17 @@
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>medicationadministration</t>
+          <t>medicationstatement</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>medadm_medication_system</t>
+          <t>medstat_medication_code</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>Codesystem der referenzierten Medication</t>
+          <t>Code der referenzierten Medication</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -3719,87 +3719,6 @@
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>medicationadministration</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>medadm_medication_code</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>Code der referenzierten Medication</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>varchar</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>medicationstatement</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>medstat_medication_system</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>Codesystem der referenzierten Medication</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>varchar</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>keep</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>medicationstatement</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>medstat_medication_code</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>Code der referenzierten Medication</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>varchar</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>keep</t>
         </is>

--- a/R-cds2db/cds2db/inst/extdata/Table_Description_Definition.xlsx
+++ b/R-cds2db/cds2db/inst/extdata/Table_Description_Definition.xlsx
@@ -3463,7 +3463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="12" min="1" max="1"/>
@@ -3719,6 +3719,60 @@
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>fall</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>fall_age_at_admission</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>Alter bei Aufnahme des Falls in abgeschlossenen Jahren</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>encounter</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>enc_age_at_admission</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Alter bei Beginn des Encounters in abgeschlossenen Jahren</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>keep</t>
         </is>

--- a/R-cds2db/cds2db/inst/extdata/Table_Description_Definition.xlsx
+++ b/R-cds2db/cds2db/inst/extdata/Table_Description_Definition.xlsx
@@ -3463,7 +3463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="12" min="1" max="1"/>
@@ -3773,6 +3773,87 @@
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>observation</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>value_in_reference_unit</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Observation-Wert in der Referenzeinheit aus der LOINC-Mapping-Tabelle</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>observation</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>reference_unit</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>Referenzeinheit aus der LOINC-Mapping-Tabelle</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>observation</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>primary_loinc_code</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>Primärer LOINC aus der LOINC-Mapping-Tabelle</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>varchar</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>keep</t>
         </is>

--- a/R-cds2db/cds2db/inst/extdata/Table_Description_Definition.xlsx
+++ b/R-cds2db/cds2db/inst/extdata/Table_Description_Definition.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="303">
   <si>
     <t xml:space="preserve">RESOURCE</t>
   </si>
@@ -847,9 +847,6 @@
     <t xml:space="preserve">ward_name</t>
   </si>
   <si>
-    <t xml:space="preserve">Stationsname</t>
-  </si>
-  <si>
     <t xml:space="preserve">varchar</t>
   </si>
   <si>
@@ -859,18 +856,12 @@
     <t xml:space="preserve">patient_id</t>
   </si>
   <si>
-    <t xml:space="preserve">Patient ID</t>
-  </si>
-  <si>
     <t xml:space="preserve">cryptoHash</t>
   </si>
   <si>
     <t xml:space="preserve">encounter_id</t>
   </si>
   <si>
-    <t xml:space="preserve">Fall ID</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dieses Blatt beschreibt Snapshot-spezifische Anreicherungsspalten.</t>
   </si>
   <si>
@@ -934,25 +925,31 @@
     <t xml:space="preserve">observation</t>
   </si>
   <si>
-    <t xml:space="preserve">value_in_reference_unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observation-Wert in der Referenzeinheit aus der LOINC-Mapping-Tabelle</t>
+    <t xml:space="preserve">analysis_loinc_code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOINC-Code für die Auswertung: primärer LOINC aus dem Mapping, sonst ursprünglicher LOINC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analysis_unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einheit des Analysewerts: Referenzeinheit bei erfolgreicher Umrechnung, sonst ursprüngliche Einheit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">analysis_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analysewert in der Analyse-Einheit: umgerechneter Wert, sonst ursprünglicher Observation-Wert</t>
   </si>
   <si>
     <t xml:space="preserve">double</t>
   </si>
   <si>
-    <t xml:space="preserve">reference_unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referenzeinheit aus der LOINC-Mapping-Tabelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">primary_loinc_code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primärer LOINC aus der LOINC-Mapping-Tabelle</t>
+    <t xml:space="preserve">analysis_value_status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status der Herkunft des Analysewerts und der verwendeten Einheit</t>
   </si>
 </sst>
 </file>
@@ -1055,7 +1052,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1069,10 +1066,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2560,7 +2553,7 @@
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C220" s="4" t="s">
+      <c r="C220" s="3" t="s">
         <v>153</v>
       </c>
     </row>
@@ -2593,10 +2586,10 @@
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A227" s="5" t="s">
+      <c r="A227" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B227" s="5" t="s">
+      <c r="B227" s="4" t="s">
         <v>161</v>
       </c>
       <c r="E227" s="1" t="s">
@@ -2604,10 +2597,10 @@
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A228" s="5" t="s">
+      <c r="A228" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="B228" s="5" t="s">
+      <c r="B228" s="4" t="s">
         <v>164</v>
       </c>
       <c r="E228" s="1" t="s">
@@ -2615,10 +2608,10 @@
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A229" s="5" t="s">
+      <c r="A229" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="B229" s="5" t="s">
+      <c r="B229" s="4" t="s">
         <v>167</v>
       </c>
       <c r="E229" s="1" t="s">
@@ -2626,10 +2619,10 @@
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A230" s="5" t="s">
+      <c r="A230" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B230" s="5" t="s">
+      <c r="B230" s="4" t="s">
         <v>170</v>
       </c>
       <c r="E230" s="1" t="s">
@@ -2637,10 +2630,10 @@
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A231" s="5" t="s">
+      <c r="A231" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B231" s="5" t="s">
+      <c r="B231" s="4" t="s">
         <v>173</v>
       </c>
       <c r="E231" s="1" t="s">
@@ -2648,10 +2641,10 @@
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A232" s="5" t="s">
+      <c r="A232" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B232" s="5" t="s">
+      <c r="B232" s="4" t="s">
         <v>176</v>
       </c>
       <c r="E232" s="1" t="s">
@@ -2659,10 +2652,10 @@
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A233" s="5" t="s">
+      <c r="A233" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="B233" s="5" t="s">
+      <c r="B233" s="4" t="s">
         <v>179</v>
       </c>
       <c r="E233" s="1" t="s">
@@ -3454,7 +3447,7 @@
       <c r="A4" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3497,7 +3490,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>255</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -3569,44 +3562,44 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>265</v>
       </c>
     </row>
@@ -3620,84 +3613,84 @@
       <c r="C5" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="6" s="6" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="6" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="7" s="6" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="7" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3726,250 +3719,267 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="D7" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D8" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="B9" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="C8" s="8" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="C10" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="C11" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="D10" s="8" t="s">
+      <c r="C12" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="C13" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="D12" s="8" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+      <c r="D15" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D16" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="B16" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="E17" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="C18" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>269</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
